--- a/file/Windows_App_for_Quest_Oculus_VR_VPATJ16954.xlsx
+++ b/file/Windows_App_for_Quest_Oculus_VR_VPATJ16954.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52E4E2CF-7B1A-4BAC-BB08-C6C82F51C91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{075957DF-31FC-4433-B76B-426A8D36C511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{52E4A011-0125-479F-9E7C-5C0437C5D876}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{1ECBE0E0-1B6A-47BB-AB30-E0BF547DB757}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年9月17日</t>
+    <t>作成日：2026年10月14日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1933,8 +1933,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A60EDB-66E5-46C1-9F3E-9FBF6952AB40}">
-  <sheetPr codeName="Sheet370">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1212C7-084D-49C1-938E-9B721883C3F0}">
+  <sheetPr codeName="Sheet407">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2749,7 +2749,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{6E7B443A-ED18-4689-8A3C-E52014A27D46}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{57FECBF2-3BBB-44C0-A4AD-2FE83963831E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2757,7 +2757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6AA296-CE97-47DC-8A3C-9A245803BC2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C27D44D-247E-4619-B6B7-2ACD774932BD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
